--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -474,7 +474,7 @@
     <t>bodyStructure</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_BodyStructure_eCS}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_BodyStructure_eCS|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -544,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -574,7 +574,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -656,7 +656,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -681,7 +681,7 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -990,7 +990,7 @@
     <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>Observation.category:third.id</t>
@@ -1054,7 +1054,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1120,7 +1120,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1149,7 +1149,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1170,7 +1170,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1254,7 +1254,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1292,7 +1292,7 @@
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalFundamentalStatus_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalFundamentalStatus_VS|1.3.0-dev</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1330,7 +1330,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1360,7 +1360,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1411,7 +1411,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1441,7 +1441,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1453,7 +1453,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1478,7 +1478,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1553,7 +1553,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1603,7 +1603,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1636,7 +1636,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1673,7 +1673,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1693,7 +1693,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -2143,7 +2143,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.5" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -474,7 +474,7 @@
     <t>bodyStructure</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_BodyStructure_eCS|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_BodyStructure_eCS}
 </t>
   </si>
   <si>
@@ -544,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -574,7 +574,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -656,7 +656,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -681,7 +681,7 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -990,7 +990,7 @@
     <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:third.id</t>
@@ -1054,7 +1054,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1120,7 +1120,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1149,7 +1149,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1170,7 +1170,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1254,7 +1254,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1292,7 +1292,7 @@
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalFundamentalStatus_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalFundamentalStatus_VS</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1330,7 +1330,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1360,7 +1360,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1411,7 +1411,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1441,7 +1441,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1453,7 +1453,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1478,7 +1478,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1553,7 +1553,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1603,7 +1603,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1636,7 +1636,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1673,7 +1673,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1693,7 +1693,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence)
 </t>
   </si>
   <si>
@@ -2143,7 +2143,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="68.5" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.51171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
